--- a/backend/data/templates/Feedback_Template.xlsx
+++ b/backend/data/templates/Feedback_Template.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Questions" sheetId="5" r:id="rId1"/>
     <sheet name="Answers" sheetId="6" r:id="rId2"/>
     <sheet name="Languages" sheetId="4" r:id="rId3"/>
+    <sheet name="Legend" sheetId="7" r:id="rIdLegend1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Answers!$A$1:$I$29</definedName>
@@ -434,7 +435,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,8 +482,68 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -507,8 +568,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B4FC4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E6F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B4FC4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E6F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -531,11 +616,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -553,6 +668,40 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -886,6 +1035,1282 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/legend.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF5B4FC4"/>
+  </sheetPr>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="5" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feedback kit version — how to fill in this template</t>
+        </is>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• This sheet is documentation only: it is ignored by the import. You can keep it in the file you upload.</t>
+        </is>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Do not rename the sheets or the column headers: they are matched exactly (case-sensitive).</t>
+        </is>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Each question has one row per language, all with the same question ID. Question-level settings (order, type, scoring, groups, skip logic) are read from the first row of each question.</t>
+        </is>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• The "Languages" sheet updates the platform-wide language list, and answer profiles are shared by every kit: a change there applies everywhere.</t>
+        </is>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet "Questions"</t>
+        </is>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What to enter</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="33" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Questions</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question_ID</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text code of the question (e.g. "SD00001").</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same code on every language row of the question. Use text codes, not plain numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Questions</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language name, for readability only.</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not read by the import: Language_ID is what counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Questions</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language_ID</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID of the language from the "Languages" sheet.</t>
+        </is>
+      </c>
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Questions</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Question" or "Disclaimer".</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A question with no rows in "Answers" is shown as information text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Questions</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question_Order</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Whole number: position of the question.</t>
+        </is>
+      </c>
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Questions</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parent / Operator / Value</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Condition to show the question.</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">See "Skip logic" below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Questions</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question_Text</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text of the question in this language. HTML allowed.</t>
+        </is>
+      </c>
+      <c r="E16" s="20"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet "Answers"</t>
+        </is>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One row per answer option and language. A question with a single input (Text, Integer, Number, Date) has one row.</t>
+        </is>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What to enter</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answers</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Progressive row number.</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not used by the import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answers</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question_ID</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question_ID of the question this option belongs to.</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Must exist in "Questions", otherwise the row is ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answers</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language name, for readability only.</t>
+        </is>
+      </c>
+      <c r="E23" s="20"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answers</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language_ID</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID of the language from the "Languages" sheet.</t>
+        </is>
+      </c>
+      <c r="E24" s="20"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answers</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Order</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Whole number: display order of the option.</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It is also the number that skip logic compares with Value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answers</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer type: Radio Button, Multiple Choice, Multiple Choice+Text, Text, Number or Date.</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">See "Answer types" below. Not case-sensitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="33" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answers</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Min</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lowest accepted value.</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only for Integer, Number and Date (for Date: a year, e.g. 1900). Must be a number; whole number for Integer and Date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="33" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answers</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Max</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Highest accepted value.</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same rules as Min. Min must not be greater than Max. Invalid bounds block the upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answers</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Label of the option shown to the patient.</t>
+        </is>
+      </c>
+      <c r="E29" s="20"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer types (Type column of "Answers")</t>
+        </is>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What the patient sees</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Min / Max</t>
+        </is>
+      </c>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radio Button</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single choice among the question's options.</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not allowed</t>
+        </is>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Checkbox" behaves the same (single choice).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multiple Choice</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check boxes: the patient can select several options.</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not allowed</t>
+        </is>
+      </c>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One row per option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="33" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multiple Choice+Text</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A check box that shows a free-text box while ticked.</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not allowed</t>
+        </is>
+      </c>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Combine with Multiple Choice rows of the same question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-line free-text box.</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not allowed</t>
+        </is>
+      </c>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+    </row>
+    <row r="37" ht="33" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numeric field with + / − buttons; decimals allowed.</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allowed: value range</t>
+        </is>
+      </c>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+    </row>
+    <row r="38" ht="33" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calendar date picker (day, month, year).</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not applied</t>
+        </is>
+      </c>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not supported</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integer, Radio Button+Text</t>
+        </is>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">These types are not displayed in this kit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skip logic — Parent / Operator / Value</t>
+        </is>
+      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A question with a Parent is shown only when the condition on the parent's answer is true. Leave Parent and Operator blank for a question that is always shown.</t>
+        </is>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value to enter</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Example</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="33" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=  (or ==)</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equal to</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer value, or the option label</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value 1 → shown if the answer with value 1 is selected</t>
+        </is>
+      </c>
+      <c r="E44" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For Multiple Choice parents: shown if that option is among the selected ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="33" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!=</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Different from</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer value, or the option label</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value 1 → shown if any other answer is selected</t>
+        </is>
+      </c>
+      <c r="E45" s="20"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Greater than</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value 2 → shown for answers 3, 4, …</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numeric comparison only. Not available for Multiple Choice parents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Less than</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value 3 → shown for answers 1, 2</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numeric comparison only. Not available for Multiple Choice parents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;=</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Greater than or equal to</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value 3 → shown for answers 3, 4, …</t>
+        </is>
+      </c>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numeric comparison only. Not available for Multiple Choice parents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;=</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Less than or equal to</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value 2 → shown for answers 1, 2</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numeric comparison only. Not available for Multiple Choice parents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="33" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IN</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One of a list</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numbers separated by ";"</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value 2;3 → shown if answer 2 or 3 is selected</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Write IN in capitals. No commas or decimals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is null</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The parent was not answered</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leave blank</t>
+        </is>
+      </c>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A skipped question counts as not answered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is not null</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The parent was answered</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leave blank</t>
+        </is>
+      </c>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skip logic — how Parent and Value are read</t>
+        </is>
+      </c>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rule</t>
+        </is>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="33" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parent</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question_ID of the question whose answer decides visibility.</t>
+        </is>
+      </c>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Case-sensitive. If the parent is not found, the question is never shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="33" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value (number)</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The "Order" of the option in the "Answers" sheet.</t>
+        </is>
+      </c>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+    </row>
+    <row r="58" ht="33" customHeight="1">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value (text)</t>
+        </is>
+      </c>
+      <c r="B58" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The option label in the patient's language (not case-sensitive).</t>
+        </is>
+      </c>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Works with = and != only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="33" customHeight="1">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chains</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If the parent is itself hidden, the question is hidden too.</t>
+        </is>
+      </c>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet "Languages"</t>
+        </is>
+      </c>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What to enter</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="33" customHeight="1">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Languages</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numeric ID of the language.</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This is the value to use in every Language_ID column. Rows without a numeric ID are skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="33" customHeight="1">
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Languages</t>
+        </is>
+      </c>
+      <c r="B64" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English name of the language.</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This name is what the survey imports (presentations, privacy policies, …) match in their "language" column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Languages</t>
+        </is>
+      </c>
+      <c r="B65" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Original_Language</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name of the language in the language itself (e.g. "Italiano").</t>
+        </is>
+      </c>
+      <c r="E65" s="20"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Languages</t>
+        </is>
+      </c>
+      <c r="B66" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alphabet</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Writing system (e.g. "Latin", "Cyrillic", "Greek").</t>
+        </is>
+      </c>
+      <c r="E66" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A61:E61"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2677DB9-CA9A-428E-BDAE-CEC3BDD279D5}">
   <dimension ref="A1:I14"/>
